--- a/marketer_forms/021_sunglasses_recommendation_quiz--marketer_forms.xlsx
+++ b/marketer_forms/021_sunglasses_recommendation_quiz--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'aviator',_'value':_'aviator'}</t>
+          <t>aviator</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Aviator', 'value': 'Aviator'}</t>
+          <t>Aviator</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cat-eye',_'value':_'cat-eye'}</t>
+          <t>cat-eye</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cat-Eye', 'value': 'Cat-Eye'}</t>
+          <t>Cat-Eye</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'oversized',_'value':_'oversized'}</t>
+          <t>oversized</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Oversized', 'value': 'Oversized'}</t>
+          <t>Oversized</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'round',_'value':_'round'}</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Round', 'value': 'Round'}</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'teashade',_'value':_'teashade'}</t>
+          <t>teashade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Teashade', 'value': 'Teashade'}</t>
+          <t>Teashade</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'oval',_'value':_'oval'}</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Oval', 'value': 'Oval'}</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'heart',_'value':_'heart'}</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Heart', 'value': 'Heart'}</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'square',_'value':_'square'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Square', 'value': 'Square'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'triangular',_'value':_'triangular'}</t>
+          <t>triangular</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Triangular', 'value': 'Triangular'}</t>
+          <t>Triangular</t>
         </is>
       </c>
     </row>
@@ -939,46 +939,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'diamond',_'value':_'diamond'}</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Diamond', 'value': 'Diamond'}</t>
+          <t>Diamond</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>what_is_your_face_shape_choices</t>
+          <t>how_would_you_prefer_to_receive_your_sunglasses_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'oval',_'value':_'oval'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Oval', 'value': 'Oval'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>what_is_your_face_shape_choices</t>
+          <t>how_would_you_prefer_to_receive_your_sunglasses_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'heart',_'value':_'heart'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Heart', 'value': 'Heart'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in-person',_'value':_'in-person'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In-person', 'value': 'In-person'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1007,46 +1007,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mail',_'value':_'mail'}</t>
+          <t>in-store</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mail', 'value': 'Mail'}</t>
+          <t>In-store</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>how_would_you_prefer_to_receive_your_sunglasses_choices</t>
+          <t>preferred_price_range_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'online',_'value':_'online'}</t>
+          <t>less_than_$100</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Online', 'value': 'Online'}</t>
+          <t>Less than $100</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>how_would_you_prefer_to_receive_your_sunglasses_choices</t>
+          <t>preferred_price_range_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'in-store',_'value':_'in-store'}</t>
+          <t>$100_-_$150</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'In-store', 'value': 'In-store'}</t>
+          <t>$100 - $150</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_$100',_'value':_'less_than_$100'}</t>
+          <t>$151_-_$200</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than $100', 'value': 'Less than $100'}</t>
+          <t>$151 - $200</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'$100_-_$150',_'value':_'$100_-_$150'}</t>
+          <t>$201_-_$250</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '$100 - $150', 'value': '$100 - $150'}</t>
+          <t>$201 - $250</t>
         </is>
       </c>
     </row>
@@ -1092,46 +1092,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'$151_-_$200',_'value':_'$151_-_$200'}</t>
+          <t>more_than_$250</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '$151 - $200', 'value': '$151 - $200'}</t>
+          <t>More than $250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>preferred_price_range_choices</t>
+          <t>preferred_frame_color_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'$201_-_$250',_'value':_'$201_-_$250'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '$201 - $250', 'value': '$201 - $250'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>preferred_price_range_choices</t>
+          <t>preferred_frame_color_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'more_than_$250',_'value':_'more_than_$250'}</t>
+          <t>gray</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'More than $250', 'value': 'More than $250'}</t>
+          <t>Gray</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'black',_'value':_'black'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Black', 'value': 'Black'}</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'gray',_'value':_'gray'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Gray', 'value': 'Gray'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1177,46 +1177,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'brown',_'value':_'brown'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Brown', 'value': 'Brown'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>preferred_frame_color_choices</t>
+          <t>recommended_sunglasses_type_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'blue',_'value':_'blue'}</t>
+          <t>aviator</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Blue', 'value': 'Blue'}</t>
+          <t>Aviator</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>preferred_frame_color_choices</t>
+          <t>recommended_sunglasses_type_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'red',_'value':_'red'}</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Red', 'value': 'Red'}</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'aviator',_'value':_'aviator'}</t>
+          <t>oversized</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Aviator', 'value': 'Aviator'}</t>
+          <t>Oversized</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'round',_'value':_'round'}</t>
+          <t>teashade</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Round', 'value': 'Round'}</t>
+          <t>Teashade</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'oversized',_'value':_'oversized'}</t>
+          <t>cat-eye</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Oversized', 'value': 'Oversized'}</t>
+          <t>Cat-Eye</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'teashade',_'value':_'teashade'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Teashade', 'value': 'Teashade'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'cat-eye',_'value':_'cat-eye'}</t>
+          <t>triangular</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Cat-Eye', 'value': 'Cat-Eye'}</t>
+          <t>Triangular</t>
         </is>
       </c>
     </row>
@@ -1313,46 +1313,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'square',_'value':_'square'}</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Square', 'value': 'Square'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>recommended_sunglasses_type_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'id':_7,_'label':_'triangular',_'value':_'triangular'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'id': 7, 'label': 'Triangular', 'value': 'Triangular'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>recommended_sunglasses_type_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'id':_8,_'label':_'diamond',_'value':_'diamond'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'id': 8, 'label': 'Diamond', 'value': 'Diamond'}</t>
+          <t>Diamond</t>
         </is>
       </c>
     </row>
